--- a/WorkBot/main/data/order_archive/Sysco/Sysco_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Sysco/Sysco_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,615 +836,6 @@
         <v>16.17</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>4617771</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Egg Patty</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" t="n">
-        <v>47.08</v>
-      </c>
-      <c r="E23" t="n">
-        <v>564.96</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>7456025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Egg Patty - Whites</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>36.96</v>
-      </c>
-      <c r="E24" t="n">
-        <v>73.92</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1592336</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ham (Unsliced)</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="E25" t="n">
-        <v>246.24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2366607</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Liquid Egg</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="E26" t="n">
-        <v>48.61</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>7128077</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Olive - Kalamata (Pitted)</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>60.59</v>
-      </c>
-      <c r="E27" t="n">
-        <v>60.59</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1589290</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Sausage - Patty (Retail)</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="E28" t="n">
-        <v>228.9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>7351430</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Vinegar - White Wine</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>41.99</v>
-      </c>
-      <c r="E29" t="n">
-        <v>41.99</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>9035601</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>American Cheese (Sliced)</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="E30" t="n">
-        <v>124.32</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2536555</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Bacon (Pre-Cooked)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>20</v>
-      </c>
-      <c r="D31" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E31" t="n">
-        <v>632.8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>3413107</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Brie</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="E32" t="n">
-        <v>54.58</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>3031442</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Butter - Unsalted</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>91.75</v>
-      </c>
-      <c r="E33" t="n">
-        <v>91.75</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>7133036</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Chicken - Diced White &amp; Dark</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>15</v>
-      </c>
-      <c r="D34" t="n">
-        <v>45.27</v>
-      </c>
-      <c r="E34" t="n">
-        <v>679.05</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1161181</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Cream Cheese</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="E35" t="n">
-        <v>390.8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>4171902</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Manchego Cheese</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>157.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>4579587</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Mayo</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>12</v>
-      </c>
-      <c r="D37" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="E37" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>7226918</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Mozz (Sliced)</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="E38" t="n">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>4401758</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Mustard - Yellow Btl</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="E39" t="n">
-        <v>63.44</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>6985683</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Quiche - Mini (Asst)</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" t="n">
-        <v>75.45</v>
-      </c>
-      <c r="E40" t="n">
-        <v>301.8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>0128298</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Soy Milk</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="E41" t="n">
-        <v>30.77</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>6986178</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Spanakopita - Mini</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" t="n">
-        <v>69.65000000000001</v>
-      </c>
-      <c r="E42" t="n">
-        <v>208.95</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>7108577</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tortilla Strips - Bulk</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="E43" t="n">
-        <v>44.95</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>7161191</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Vegan Mozz</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>89.65000000000001</v>
-      </c>
-      <c r="E44" t="n">
-        <v>179.3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>6472502</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Yogurt - Plain (BIB)</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>4</v>
-      </c>
-      <c r="D45" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="E45" t="n">
-        <v>128.2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1073105</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Mozz (Unsliced)</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="E46" t="n">
-        <v>98.40000000000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>7770734</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Manicotti - Cheese</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
-        <v>53.49</v>
-      </c>
-      <c r="E47" t="n">
-        <v>53.49</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>7256054</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Cheddar - Orange (Unsliced)</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" t="n">
-        <v>38</v>
-      </c>
-      <c r="E48" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1735372</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Cucumber (English)</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="E49" t="n">
-        <v>54.68</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>4615704</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Pepper - Red Bell Fresh</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>59.95</v>
-      </c>
-      <c r="E50" t="n">
-        <v>59.95</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1048313</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Lime - Fresh</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="n">
-        <v>77.47</v>
-      </c>
-      <c r="E51" t="n">
-        <v>77.47</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
